--- a/Supplementary tables.xlsx
+++ b/Supplementary tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyProfile\Master\Laboratory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410B330-05AC-4640-9322-85F623677993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EB82D5-9884-4C70-92F4-2A2FF52B957F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{66A28C09-B2C5-41C2-AD92-25F9450B7144}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{66A28C09-B2C5-41C2-AD92-25F9450B7144}"/>
   </bookViews>
   <sheets>
     <sheet name="phasing" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="67">
   <si>
     <t>phased_ratio</t>
   </si>
@@ -244,9 +244,6 @@
   </si>
   <si>
     <t>lohratio</t>
-  </si>
-  <si>
-    <t>ori</t>
   </si>
   <si>
     <t>loh_detector</t>
@@ -2551,7 +2548,7 @@
         <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
         <v>21</v>
@@ -2667,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5">
         <v>0.35466769686317601</v>
@@ -2696,7 +2693,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6">
         <v>0.38938099721270802</v>
@@ -2719,7 +2716,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2748,7 +2745,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2777,7 +2774,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2806,13 +2803,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10">
         <v>0.35466769686317601</v>
@@ -2835,13 +2832,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11">
         <v>0.38938099721270802</v>
@@ -2957,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15">
         <v>0.30056954673324399</v>
@@ -2986,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16">
         <v>0.33664021170857</v>
@@ -3009,7 +3006,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -3038,7 +3035,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -3067,7 +3064,7 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -3096,13 +3093,13 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E20">
         <v>0.30044058949955199</v>
@@ -3125,13 +3122,13 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21">
         <v>0.33486952117024599</v>
@@ -3247,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E25">
         <v>0.391252437626327</v>
@@ -3276,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>0.43664912205366802</v>
@@ -3299,7 +3296,7 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -3328,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -3357,7 +3354,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -3386,13 +3383,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30">
         <v>0.38725336092492402</v>
@@ -3415,13 +3412,13 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31">
         <v>0.45285402667265501</v>
@@ -3537,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E35">
         <v>0.38420401187437098</v>
@@ -3566,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E36">
         <v>0.45359919717436298</v>
@@ -3589,7 +3586,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -3618,7 +3615,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -3647,7 +3644,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3676,13 +3673,13 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E40">
         <v>0.36882590305430302</v>
@@ -3705,13 +3702,13 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E41">
         <v>0.42826420788543101</v>
@@ -3827,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45">
         <v>0.49643408592937999</v>
@@ -3856,7 +3853,7 @@
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E46">
         <v>0.59679921669879399</v>
@@ -3879,7 +3876,7 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -3908,7 +3905,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -3937,7 +3934,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -3966,13 +3963,13 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E50">
         <v>0.501779841668334</v>
@@ -3995,13 +3992,13 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E51">
         <v>0.57767069918884895</v>
@@ -4117,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E55">
         <v>0.4834883975691</v>
@@ -4146,7 +4143,7 @@
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E56">
         <v>0.54000135818573103</v>
@@ -4169,7 +4166,7 @@
         <v>13</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -4198,7 +4195,7 @@
         <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -4227,7 +4224,7 @@
         <v>13</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -4256,13 +4253,13 @@
         <v>13</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>0.50652467416306801</v>
@@ -4285,13 +4282,13 @@
         <v>13</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E61">
         <v>0.555268993590741</v>
@@ -4407,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E65">
         <v>0.55008321614773004</v>
@@ -4436,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E66">
         <v>0.56536847092201703</v>
@@ -4459,7 +4456,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -4488,7 +4485,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -4517,7 +4514,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -4546,13 +4543,13 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E70">
         <v>0.54335124342169805</v>
@@ -4575,13 +4572,13 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E71">
         <v>0.56077472489771296</v>
@@ -4697,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E75" t="s">
         <v>60</v>
@@ -4726,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E76">
         <v>0.52630694362408803</v>
@@ -4749,7 +4746,7 @@
         <v>15</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -4778,7 +4775,7 @@
         <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -4807,7 +4804,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -4836,13 +4833,13 @@
         <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E80" t="s">
         <v>60</v>
@@ -4865,13 +4862,13 @@
         <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E81">
         <v>0.543373837618223</v>
@@ -14217,7 +14214,7 @@
         <v>0.99</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -14234,7 +14231,7 @@
         <v>0.84</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -14329,7 +14326,7 @@
         <v>0.99</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -14346,7 +14343,7 @@
         <v>0.84</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -14441,7 +14438,7 @@
         <v>0.76</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -14458,7 +14455,7 @@
         <v>0.78</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -14553,7 +14550,7 @@
         <v>0.54</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -14570,7 +14567,7 @@
         <v>0.59</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -14665,7 +14662,7 @@
         <v>0.4</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -14682,7 +14679,7 @@
         <v>0.74</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -14777,7 +14774,7 @@
         <v>0.42</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -14794,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -14889,7 +14886,7 @@
         <v>0.98</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -14906,7 +14903,7 @@
         <v>0.93</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -15001,7 +14998,7 @@
         <v>0.99</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -15018,7 +15015,7 @@
         <v>0.96</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -15113,7 +15110,7 @@
         <v>0.78</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -15130,7 +15127,7 @@
         <v>0.81</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -15225,7 +15222,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -15242,7 +15239,7 @@
         <v>0.61</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -15337,7 +15334,7 @@
         <v>0.38</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -15354,7 +15351,7 @@
         <v>0.95</v>
       </c>
       <c r="E53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -15449,7 +15446,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -15466,7 +15463,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -15561,7 +15558,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -15578,7 +15575,7 @@
         <v>0.96</v>
       </c>
       <c r="E63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -15673,7 +15670,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -15690,7 +15687,7 @@
         <v>0.94</v>
       </c>
       <c r="E68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -15785,7 +15782,7 @@
         <v>0.79</v>
       </c>
       <c r="E72" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -15802,7 +15799,7 @@
         <v>0.81</v>
       </c>
       <c r="E73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -15897,7 +15894,7 @@
         <v>0.6</v>
       </c>
       <c r="E77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -15914,7 +15911,7 @@
         <v>0.67</v>
       </c>
       <c r="E78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -16009,7 +16006,7 @@
         <v>0.41</v>
       </c>
       <c r="E82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -16023,7 +16020,7 @@
         <v>0.4</v>
       </c>
       <c r="E83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -16118,7 +16115,7 @@
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -16135,7 +16132,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -16230,7 +16227,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -16247,7 +16244,7 @@
         <v>0.99</v>
       </c>
       <c r="E93" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -16342,7 +16339,7 @@
         <v>0.99</v>
       </c>
       <c r="E97" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -16359,7 +16356,7 @@
         <v>0.98</v>
       </c>
       <c r="E98" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -16454,7 +16451,7 @@
         <v>0.83</v>
       </c>
       <c r="E102" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -16471,7 +16468,7 @@
         <v>0.86</v>
       </c>
       <c r="E103" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -16566,7 +16563,7 @@
         <v>0.65</v>
       </c>
       <c r="E107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -16583,7 +16580,7 @@
         <v>0.71</v>
       </c>
       <c r="E108" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -16678,7 +16675,7 @@
         <v>0.45</v>
       </c>
       <c r="E112" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -16695,7 +16692,7 @@
         <v>0.88</v>
       </c>
       <c r="E113" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -16790,7 +16787,7 @@
         <v>0.32</v>
       </c>
       <c r="E117" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -16807,7 +16804,7 @@
         <v>0.97</v>
       </c>
       <c r="E118" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -16902,7 +16899,7 @@
         <v>0.99</v>
       </c>
       <c r="E122" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -16919,7 +16916,7 @@
         <v>0.95</v>
       </c>
       <c r="E123" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -17014,7 +17011,7 @@
         <v>0.99</v>
       </c>
       <c r="E127" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -17031,7 +17028,7 @@
         <v>0.92</v>
       </c>
       <c r="E128" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -17126,7 +17123,7 @@
         <v>0.73</v>
       </c>
       <c r="E132" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -17143,7 +17140,7 @@
         <v>0.8</v>
       </c>
       <c r="E133" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -17238,7 +17235,7 @@
         <v>0.6</v>
       </c>
       <c r="E137" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -17255,7 +17252,7 @@
         <v>0.68</v>
       </c>
       <c r="E138" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -17350,7 +17347,7 @@
         <v>0.49</v>
       </c>
       <c r="E142" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -17367,7 +17364,7 @@
         <v>0.95</v>
       </c>
       <c r="E143" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -17462,7 +17459,7 @@
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -17479,7 +17476,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -17574,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -17591,7 +17588,7 @@
         <v>0.97</v>
       </c>
       <c r="E153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -17686,7 +17683,7 @@
         <v>0.98</v>
       </c>
       <c r="E157" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -17703,7 +17700,7 @@
         <v>0.9</v>
       </c>
       <c r="E158" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -17798,7 +17795,7 @@
         <v>0.79</v>
       </c>
       <c r="E162" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -17815,7 +17812,7 @@
         <v>0.82</v>
       </c>
       <c r="E163" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -17910,7 +17907,7 @@
         <v>0.65</v>
       </c>
       <c r="E167" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -17927,7 +17924,7 @@
         <v>0.69</v>
       </c>
       <c r="E168" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -18022,7 +18019,7 @@
         <v>0.49</v>
       </c>
       <c r="E172" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -18039,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
@@ -18134,7 +18131,7 @@
         <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -18151,7 +18148,7 @@
         <v>0.9</v>
       </c>
       <c r="E178" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -18246,7 +18243,7 @@
         <v>1</v>
       </c>
       <c r="E182" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -18263,7 +18260,7 @@
         <v>0.95</v>
       </c>
       <c r="E183" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -18358,7 +18355,7 @@
         <v>0.99</v>
       </c>
       <c r="E187" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -18375,7 +18372,7 @@
         <v>0.92</v>
       </c>
       <c r="E188" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -18470,7 +18467,7 @@
         <v>0.78</v>
       </c>
       <c r="E192" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -18487,7 +18484,7 @@
         <v>0.8</v>
       </c>
       <c r="E193" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -18582,7 +18579,7 @@
         <v>0.59</v>
       </c>
       <c r="E197" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -18596,7 +18593,7 @@
         <v>0.6</v>
       </c>
       <c r="E198" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -18691,7 +18688,7 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -18708,7 +18705,7 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -18803,7 +18800,7 @@
         <v>1</v>
       </c>
       <c r="E207" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -18820,7 +18817,7 @@
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -18915,7 +18912,7 @@
         <v>60</v>
       </c>
       <c r="E212" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -18932,7 +18929,7 @@
         <v>0.73</v>
       </c>
       <c r="E213" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -19027,7 +19024,7 @@
         <v>60</v>
       </c>
       <c r="E217" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -19044,7 +19041,7 @@
         <v>0.69</v>
       </c>
       <c r="E218" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -19139,7 +19136,7 @@
         <v>60</v>
       </c>
       <c r="E222" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -19156,7 +19153,7 @@
         <v>60</v>
       </c>
       <c r="E223" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -19251,7 +19248,7 @@
         <v>60</v>
       </c>
       <c r="E227" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -19268,7 +19265,7 @@
         <v>60</v>
       </c>
       <c r="E228" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -19363,7 +19360,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
@@ -19380,7 +19377,7 @@
         <v>1</v>
       </c>
       <c r="E233" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
@@ -19475,7 +19472,7 @@
         <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
@@ -19492,7 +19489,7 @@
         <v>1</v>
       </c>
       <c r="E238" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
